--- a/output/graficos_dimensiones/comunal_p_basica_a_2021_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_p_basica_a_2021_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:43</t>
+    <t xml:space="preserve">2026-09-09 23:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_basica_a_2021_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_p_basica_a_2021_coquimbo.xlsx
@@ -69,15 +69,15 @@
     <t xml:space="preserve">Ovalle</t>
   </si>
   <si>
+    <t xml:space="preserve">Paihuano</t>
+  </si>
+  <si>
     <t xml:space="preserve">Vicuña</t>
   </si>
   <si>
     <t xml:space="preserve">La Serena</t>
   </si>
   <si>
-    <t xml:space="preserve">Paihuano</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:42</t>
+    <t xml:space="preserve">2026-09-18 10:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -704,13 +704,13 @@
         <v>17</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>4106</v>
+        <v>4105</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>16.48</v>
+        <v>16.49</v>
       </c>
     </row>
     <row r="14">
@@ -718,16 +718,16 @@
         <v>5</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>4102</v>
+        <v>4106</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>16.19</v>
+        <v>16.48</v>
       </c>
     </row>
     <row r="15">
@@ -735,16 +735,16 @@
         <v>5</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>4101</v>
+        <v>4102</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>13.82</v>
+        <v>16.19</v>
       </c>
     </row>
     <row r="16">
@@ -755,10 +755,14 @@
         <v>19</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>4105</v>
-      </c>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
+        <v>4101</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>13.82</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E16"/>

--- a/output/graficos_dimensiones/comunal_p_basica_a_2021_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_p_basica_a_2021_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:31</t>
+    <t xml:space="preserve">2026-09-23 13:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_basica_a_2021_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_p_basica_a_2021_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 13:03</t>
+    <t xml:space="preserve">2026-10-02 15:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_basica_a_2021_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_p_basica_a_2021_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:34</t>
+    <t xml:space="preserve">2026-10-04 09:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_basica_a_2021_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_p_basica_a_2021_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 09:48</t>
+    <t xml:space="preserve">2026-10-05 13:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
